--- a/tsmc/dist/20261028_台積電個股模型_v0.4.xlsx
+++ b/tsmc/dist/20261028_台積電個股模型_v0.4.xlsx
@@ -10989,7 +10989,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/memory</t>
+      <t xml:space="preserve">Siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -11010,16 +11010,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/memory Mkt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：需求 </t>
+      <t xml:space="preserve">Siliconomics SIF_HBM_GapEB_A ÷ SIF_HBM_SupplyEB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：需求 </t>
     </r>
     <r>
       <rPr>
@@ -39242,7 +39261,7 @@
         <v>42</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0.21</v>
+        <v>0.210219254415343</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>128</v>
@@ -42095,7 +42114,7 @@
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">hbm_gap27</f>
-        <v>0.21</v>
+        <v>0.210219254415343</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>554</v>

--- a/tsmc/dist/20261028_台積電個股模型_v0.4.xlsx
+++ b/tsmc/dist/20261028_台積電個股模型_v0.4.xlsx
@@ -270,7 +270,9 @@
     <definedName function="false" hidden="false" name="rev26_4q_lo" vbProcedure="false">In!$D$82</definedName>
     <definedName function="false" hidden="false" name="rev26_hi" vbProcedure="false">In!$F$102</definedName>
     <definedName function="false" hidden="false" name="rev26_lo" vbProcedure="false">In!$D$102</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$135</definedName>
     <definedName function="false" hidden="false" name="shares" vbProcedure="false">In!$E$165</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$136</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$183</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$182</definedName>
     <definedName function="false" hidden="false" name="tp_roe" vbProcedure="false">In!$E$184</definedName>
@@ -319,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="981">
   <si>
     <r>
       <rPr>
@@ -3674,26 +3676,759 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NT$2,446</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相同（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">137.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），分歧從 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開始：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 157.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 129.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 106.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境價值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,769</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,041</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,496</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收（持平 → −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）與毛利率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60% → −7.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67% → +5.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）最敏感。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：資本支出不隨情境下修（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">皆為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">十億美元），情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的自由現金流降得比淨利快：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自由現金流 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 84.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 57.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 34.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">十億美元（淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">127.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">104.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS ×</t>
     </r>
     <r>
       <rPr>
@@ -3712,7 +4447,370 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF 2,150</t>
+      <t xml:space="preserve">1 − g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）未扣資本支出，偏高估。下一個檢驗事件是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中旬）的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出與毛利率指引；折現率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±1pt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使加權目標價 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -3731,1235 +4829,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 2,742 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,385</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0%–25%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單獨為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。與共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,390 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的差距主要是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個月後前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 134.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，倍數因素只 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（共識目標價隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍，同業中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相同（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">137.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），分歧從 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">開始：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 157.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 129.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 106.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">58%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">54%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境價值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,769</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,041</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,496</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">對非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收（持平 → −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）與毛利率（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60% → −7.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">67% → +5.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）最敏感。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：資本支出不隨情境下修（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2029 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">皆為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">95 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">十億美元），情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的自由現金流降得比淨利快：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自由現金流 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 84.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 57.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 34.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">十億美元（淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">127.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">104.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">86.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">用 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS ×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 − g</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）未扣資本支出，偏高估。下一個檢驗事件是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027-01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中旬）的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資本支出與毛利率指引；折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±1pt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使加權目標價 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+8.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -29976,973 +29874,13 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Recon — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司口徑、共識（只作事後對照）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本模型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">對照值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差距</t>
-  </si>
-  <si>
-    <t xml:space="preserve">對照來源</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相關營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司口徑推算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速器十幾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">後段 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× CAGR 57%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（公司）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速器內容（不含其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相關（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ai_oth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 EPS vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司全年成長指引（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 × (1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法說：全年美元成長約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 EPS vs 1–3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實績＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">指引推算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司各季 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 22.08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">27.25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">29.43</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">指引中點</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 CoWoS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需求 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs Morgan Stanley</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 CoWoS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需求 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs Morgan Stanley</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-25 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">擷取）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MarketScreener </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">預估頁；第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節差距拆解用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-25 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">擷取）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — 2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：一次動一個輸入</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">輸入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2027 CoWoS </t>
+      <t xml:space="preserve">0.5 </t>
     </r>
     <r>
       <rPr>
@@ -30951,7 +29889,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">需求 </t>
+      <t xml:space="preserve">相對倍數調整（</t>
     </r>
     <r>
       <rPr>
@@ -30961,7 +29899,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -30970,230 +29908,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">產能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">內容價格 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 +0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（不漲）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 60%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 67%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 +0%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoWoS 2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底產能 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">萬片（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">KGI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
     </r>
     <r>
       <rPr>
@@ -31203,7 +29918,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">× </t>
     </r>
     <r>
       <rPr>
@@ -31212,7 +29927,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營業利益 對 </t>
+      <t xml:space="preserve">本公司 </t>
     </r>
     <r>
       <rPr>
@@ -31222,7 +29937,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">EPS </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -31231,7 +29946,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的影響（情境 </t>
+      <t xml:space="preserve">年相對同業的 </t>
     </r>
     <r>
       <rPr>
@@ -31241,7 +29956,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">P/E </t>
     </r>
     <r>
       <rPr>
@@ -31250,128 +29965,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">比值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028 EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基準（推導值）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.864</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（低）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.909</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（高）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標價參數（只改 </t>
+      <t xml:space="preserve">比；</t>
     </r>
     <r>
       <rPr>
@@ -31381,7 +29975,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
     </r>
     <r>
       <rPr>
@@ -31390,8 +29984,345 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">參數；</t>
-    </r>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -31400,7 +30331,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -31409,8 +30340,647 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頁收斂法的 </t>
-    </r>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台積電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2330.TW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2330 TT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2303.TW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2303 TT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg GFS US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg INTC US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 0981 HK Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 005930 KS Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -31419,7 +30989,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">fade_g </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -31428,8 +30998,1019 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不隨 </t>
-    </r>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Recon — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司口徑、共識（只作事後對照）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本模型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">對照值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">差距</t>
+  </si>
+  <si>
+    <t xml:space="preserve">對照來源</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相關營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司口徑推算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速器十幾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後段 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× CAGR 57%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（公司）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速器內容（不含其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相關（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ai_oth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 EPS vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司全年成長指引（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 × (1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法說：全年美元成長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 EPS vs 1–3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實績＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">指引推算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS 22.08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">指引中點</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需求 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs Morgan Stanley</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需求 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs Morgan Stanley</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">擷取）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MarketScreener </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">預估頁；第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節差距拆解用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">擷取）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — 2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：一次動一個輸入</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">輸入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -31438,7 +32019,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tp_g </t>
+      <t xml:space="preserve">2027 CoWoS </t>
     </r>
     <r>
       <rPr>
@@ -31447,13 +32028,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">變動）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案例</t>
-  </si>
-  <si>
+      <t xml:space="preserve">需求 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -31462,7 +32038,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">÷ </t>
     </r>
     <r>
       <rPr>
@@ -31471,10 +32047,231 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">產能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">內容價格 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 +0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不漲）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 60%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 67%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 +0%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoWoS 2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底產能 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">萬片（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -31483,7 +32280,266 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable </t>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 對 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的影響（情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028 EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基準（推導值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.864</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（低）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.909</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（高）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價參數（只改 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參數；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁收斂法的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">fade_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不隨 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tp_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變動）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案例</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
     </r>
     <r>
       <rPr>
@@ -37009,7 +38065,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -37020,7 +38076,8 @@
     <numFmt numFmtId="171" formatCode="0.00"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
     <numFmt numFmtId="173" formatCode="@"/>
-    <numFmt numFmtId="174" formatCode="0.000000"/>
+    <numFmt numFmtId="174" formatCode="0"/>
+    <numFmt numFmtId="175" formatCode="0.000000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -37143,7 +38200,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -37261,6 +38318,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -37520,7 +38585,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -37624,17 +38689,23 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>17</v>
+      <c r="A21" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 NT$"&amp;TEXT(Val!$B$94,"#,##0")&amp;"（DCF "&amp;TEXT(Val!$B$79,"#,##0")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0")&amp;"（2026-10-22）"&amp;IF(Val!$B$97&gt;=0,"高 "&amp;TEXT(Val!$B$97,"0.0%"),"低 "&amp;TEXT(-Val!$B$97,"0.0%"))&amp;"，級距 "&amp;Val!$B$115&amp;"、投資建議 "&amp;Val!$B$116&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$79+(1-tp_w_dcf)*Val!$B$90)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$98,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：與共識目標價 3,390 的差距主要是 EPS：本模型 12 個月後前瞻 EPS 134.0 比共識前瞻 EPS 低 26.2%，倍數因素只 −8.7%（共識目標價隱含 18.7 倍，同業中位數 20.5 倍）。"</f>
+        <v>重點觀察 1：目標價 NT$2,803（DCF 2,155、Comparable（相對倍數調整後）3,451；DCF 權重 50%），比現價 2,385（2026-10-22）高 17.5%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.26（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +2.7%；Comparable 單獨（市場主流同業法、未調整）為 +15.1%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：與共識目標價 3,390 的差距主要是 EPS：本模型 12 個月後前瞻 EPS 134.0 比共識前瞻 EPS 低 26.2%，倍數因素只 −8.7%（共識目標價隱含 18.7 倍，同業中位數 20.5 倍）。</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>19</v>
       </c>
     </row>
@@ -43731,7 +44802,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:Q136"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -45161,8 +46232,8 @@
         <v>721</v>
       </c>
       <c r="B94" s="26" t="n">
-        <f aca="false">tp_w_dcf*B79+(1-tp_w_dcf)*B90</f>
-        <v>2450.23630789608</v>
+        <f aca="false">tp_w_dcf*B79+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>2803.49822381737</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>722</v>
@@ -45195,7 +46266,7 @@
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">B94/px-1</f>
-        <v>0.0273527496419603</v>
+        <v>0.175470953382545</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>727</v>
@@ -45401,6 +46472,478 @@
       </c>
       <c r="E116" s="4" t="s">
         <v>754</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>759</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>760</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="G121" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="H121" s="15" t="s">
+        <v>763</v>
+      </c>
+      <c r="I121" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="J121" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="K121" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="L121" s="15" t="s">
+        <v>767</v>
+      </c>
+      <c r="M121" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="N121" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="O121" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="P121" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q121" s="5" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="D122" s="24" t="n">
+        <v>14.156</v>
+      </c>
+      <c r="E122" s="24" t="n">
+        <v>16.0605</v>
+      </c>
+      <c r="F122" s="24" t="n">
+        <v>17.9995</v>
+      </c>
+      <c r="G122" s="24" t="n">
+        <v>18.751</v>
+      </c>
+      <c r="H122" s="24" t="n">
+        <v>24.5295</v>
+      </c>
+      <c r="I122" s="24" t="n">
+        <v>16.0195</v>
+      </c>
+      <c r="J122" s="24" t="n">
+        <v>14.927</v>
+      </c>
+      <c r="K122" s="24" t="n">
+        <v>18.821</v>
+      </c>
+      <c r="L122" s="24" t="n">
+        <v>17.7185</v>
+      </c>
+      <c r="M122" s="24" t="n">
+        <v>19.3025</v>
+      </c>
+      <c r="N122" s="8" t="n">
+        <f aca="false">COUNT(D122:M122)</f>
+        <v>10</v>
+      </c>
+      <c r="O122" s="23" t="n">
+        <f aca="false">IF(N122&gt;0,MEDIAN(D122:M122),"")</f>
+        <v>17.859</v>
+      </c>
+      <c r="P122" s="23" t="n">
+        <f aca="false">IF(N122&gt;=7,O122,"")</f>
+        <v>17.859</v>
+      </c>
+      <c r="Q122" s="8" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D123" s="24" t="n">
+        <v>18.5065</v>
+      </c>
+      <c r="E123" s="24" t="n">
+        <v>20.0135</v>
+      </c>
+      <c r="F123" s="24" t="n">
+        <v>20.6125</v>
+      </c>
+      <c r="G123" s="24" t="n">
+        <v>14.4285</v>
+      </c>
+      <c r="H123" s="24" t="n">
+        <v>15.9615</v>
+      </c>
+      <c r="I123" s="24" t="n">
+        <v>7.8765</v>
+      </c>
+      <c r="J123" s="24" t="n">
+        <v>10.0455</v>
+      </c>
+      <c r="K123" s="24" t="n">
+        <v>11.4775</v>
+      </c>
+      <c r="L123" s="24" t="n">
+        <v>12.522</v>
+      </c>
+      <c r="M123" s="24" t="n">
+        <v>17.0705</v>
+      </c>
+      <c r="N123" s="8" t="n">
+        <f aca="false">COUNT(D123:M123)</f>
+        <v>10</v>
+      </c>
+      <c r="O123" s="23" t="n">
+        <f aca="false">IF(N123&gt;0,MEDIAN(D123:M123),"")</f>
+        <v>15.195</v>
+      </c>
+      <c r="P123" s="23" t="n">
+        <f aca="false">IF(N123&gt;=7,O123,"")</f>
+        <v>15.195</v>
+      </c>
+      <c r="Q123" s="8" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="I124" s="24" t="n">
+        <v>25.3475</v>
+      </c>
+      <c r="J124" s="24" t="n">
+        <v>24.295</v>
+      </c>
+      <c r="K124" s="24" t="n">
+        <v>28.656</v>
+      </c>
+      <c r="L124" s="24" t="n">
+        <v>19.676</v>
+      </c>
+      <c r="M124" s="24" t="n">
+        <v>22.1005</v>
+      </c>
+      <c r="N124" s="8" t="n">
+        <f aca="false">COUNT(D124:M124)</f>
+        <v>5</v>
+      </c>
+      <c r="O124" s="23" t="n">
+        <f aca="false">IF(N124&gt;0,MEDIAN(D124:M124),"")</f>
+        <v>24.295</v>
+      </c>
+      <c r="P124" s="23" t="str">
+        <f aca="false">IF(N124&gt;=7,O124,"")</f>
+        <v/>
+      </c>
+      <c r="Q124" s="8" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D125" s="24" t="n">
+        <v>12.454</v>
+      </c>
+      <c r="E125" s="24" t="n">
+        <v>13.3745</v>
+      </c>
+      <c r="F125" s="24" t="n">
+        <v>11.224</v>
+      </c>
+      <c r="G125" s="24" t="n">
+        <v>11.8385</v>
+      </c>
+      <c r="H125" s="24" t="n">
+        <v>12.1295</v>
+      </c>
+      <c r="I125" s="24" t="n">
+        <v>13.0485</v>
+      </c>
+      <c r="J125" s="24" t="n">
+        <v>27.5115</v>
+      </c>
+      <c r="K125" s="24" t="n">
+        <v>25.866</v>
+      </c>
+      <c r="L125" s="24" t="n">
+        <v>39.641</v>
+      </c>
+      <c r="M125" s="24" t="n">
+        <v>67.9365</v>
+      </c>
+      <c r="N125" s="8" t="n">
+        <f aca="false">COUNT(D125:M125)</f>
+        <v>10</v>
+      </c>
+      <c r="O125" s="23" t="n">
+        <f aca="false">IF(N125&gt;0,MEDIAN(D125:M125),"")</f>
+        <v>13.2115</v>
+      </c>
+      <c r="P125" s="23" t="n">
+        <f aca="false">IF(N125&gt;=7,O125,"")</f>
+        <v>13.2115</v>
+      </c>
+      <c r="Q125" s="8" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D126" s="24" t="n">
+        <v>15.6775</v>
+      </c>
+      <c r="E126" s="24" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="F126" s="24" t="n">
+        <v>78.239</v>
+      </c>
+      <c r="G126" s="24" t="n">
+        <v>51.8865</v>
+      </c>
+      <c r="H126" s="24" t="n">
+        <v>41.8545</v>
+      </c>
+      <c r="I126" s="24" t="n">
+        <v>10.7145</v>
+      </c>
+      <c r="J126" s="24" t="n">
+        <v>20.6075</v>
+      </c>
+      <c r="K126" s="24" t="n">
+        <v>28.124</v>
+      </c>
+      <c r="L126" s="24" t="n">
+        <v>51.468</v>
+      </c>
+      <c r="M126" s="24" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="N126" s="8" t="n">
+        <f aca="false">COUNT(D126:M126)</f>
+        <v>10</v>
+      </c>
+      <c r="O126" s="23" t="n">
+        <f aca="false">IF(N126&gt;0,MEDIAN(D126:M126),"")</f>
+        <v>46.66125</v>
+      </c>
+      <c r="P126" s="23" t="n">
+        <f aca="false">IF(N126&gt;=7,O126,"")</f>
+        <v>46.66125</v>
+      </c>
+      <c r="Q126" s="8" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D127" s="24" t="n">
+        <v>8.3275</v>
+      </c>
+      <c r="E127" s="24" t="n">
+        <v>6.7735</v>
+      </c>
+      <c r="F127" s="24" t="n">
+        <v>11.3775</v>
+      </c>
+      <c r="G127" s="24" t="n">
+        <v>11.787</v>
+      </c>
+      <c r="H127" s="24" t="n">
+        <v>12.8055</v>
+      </c>
+      <c r="I127" s="24" t="n">
+        <v>9.5745</v>
+      </c>
+      <c r="J127" s="24" t="n">
+        <v>20.782</v>
+      </c>
+      <c r="K127" s="24" t="n">
+        <v>13.1575</v>
+      </c>
+      <c r="L127" s="24" t="n">
+        <v>11.434</v>
+      </c>
+      <c r="M127" s="24" t="n">
+        <v>6.1985</v>
+      </c>
+      <c r="N127" s="8" t="n">
+        <f aca="false">COUNT(D127:M127)</f>
+        <v>10</v>
+      </c>
+      <c r="O127" s="23" t="n">
+        <f aca="false">IF(N127&gt;0,MEDIAN(D127:M127),"")</f>
+        <v>11.40575</v>
+      </c>
+      <c r="P127" s="23" t="n">
+        <f aca="false">IF(N127&gt;=7,O127,"")</f>
+        <v>11.40575</v>
+      </c>
+      <c r="Q127" s="8" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="B129" s="23" t="n">
+        <f aca="false">P122</f>
+        <v>17.859</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="B130" s="29" t="n">
+        <f aca="false">COUNT(P123:P127)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="B131" s="23" t="n">
+        <f aca="false">IF(B130&gt;0,MEDIAN(P123:P127),"")</f>
+        <v>14.20325</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B132" s="23" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B129),B130&gt;=2),B129/B131,"")</f>
+        <v>1.25738827381057</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="B133" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="B134" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B135" s="30" t="n">
+        <f aca="false">IF(ISNUMBER(B132),MIN(MAX(B132,B133),B134),1)</f>
+        <v>1.25738827381057</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="B136" s="26" t="n">
+        <f aca="false">Val!$B$90*B135</f>
+        <v>3451.49671418364</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -45428,7 +46971,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45436,21 +46979,21 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>757</v>
+        <v>799</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>758</v>
+        <v>800</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>759</v>
+        <v>801</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>760</v>
+        <v>802</v>
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">PL!B5</f>
@@ -45465,12 +47008,12 @@
         <v>-0.00788231517711135</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>761</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>762</v>
+        <v>804</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">PL!B4</f>
@@ -45485,12 +47028,12 @@
         <v>-0.173235262647593</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>764</v>
+        <v>806</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -45510,7 +47053,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>765</v>
+        <v>807</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">PL!B7</f>
@@ -45525,12 +47068,12 @@
         <v>-0.00101645384664262</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>766</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>767</v>
+        <v>809</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -45545,12 +47088,12 @@
         <v>-5.0502654148521E-005</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>768</v>
+        <v>810</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">PL!C7</f>
@@ -45570,7 +47113,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>770</v>
+        <v>812</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -45590,7 +47133,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>771</v>
+        <v>813</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">CoWoS!B13</f>
@@ -45610,7 +47153,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">CoWoS!C13</f>
@@ -45630,7 +47173,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>773</v>
+        <v>815</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -45645,12 +47188,12 @@
         <v>-0.0704101152815759</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>774</v>
+        <v>816</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>775</v>
+        <v>817</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">PL!D13</f>
@@ -45693,21 +47236,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>776</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>777</v>
+        <v>819</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>778</v>
+        <v>820</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>780</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45729,7 +47272,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">(PL!C7-0.3*u_rb_27*ct_VR*(1+px27)*(1+ai_oth))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -45746,7 +47289,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>782</v>
+        <v>824</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">(PL!C7-PL!C5*px27/(1+px27))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -45763,7 +47306,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>783</v>
+        <v>825</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">(PL!C7)*(0.6-opex)*ni_op*fx/shares</f>
@@ -45780,7 +47323,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(PL!C7)*(0.67-opex)*ni_op*fx/shares</f>
@@ -45797,7 +47340,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>785</v>
+        <v>827</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">(PL!C7-PL!B6*na27_A)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -45814,7 +47357,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>786</v>
+        <v>828</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -45831,32 +47374,32 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>787</v>
+        <v>829</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>778</v>
+        <v>820</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>790</v>
+        <v>832</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>791</v>
+        <v>833</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">ni_op</f>
@@ -45881,7 +47424,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>792</v>
+        <v>834</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">ni_op_lo</f>
@@ -45906,7 +47449,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">ni_op_hi</f>
@@ -45931,27 +47474,27 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>794</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>795</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>796</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>797</v>
-      </c>
       <c r="E22" s="5" t="s">
-        <v>798</v>
+        <v>839</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45959,19 +47502,19 @@
         <v>25</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>799</v>
+        <v>840</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>2155.49973345111</v>
       </c>
       <c r="D23" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">tp_w_dcf*C23+(1-tp_w_dcf)*D23</f>
-        <v>2450.23630789608</v>
+        <v>2803.49822381737</v>
       </c>
       <c r="F23" s="14" t="n">
         <f aca="false">E23/E$23-1</f>
@@ -45980,153 +47523,153 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
         <v>1863.30501824391</v>
       </c>
       <c r="D24" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">tp_w_dcf*C24+(1-tp_w_dcf)*D24</f>
-        <v>2304.13895029248</v>
+        <v>2657.40086621377</v>
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">E24/E$23-1</f>
-        <v>-0.0596258234900815</v>
+        <v>-0.0521125201230438</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
         <v>2564.62239361724</v>
       </c>
       <c r="D25" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">tp_w_dcf*C25+(1-tp_w_dcf)*D25</f>
-        <v>2654.79763797914</v>
+        <v>3008.05955390044</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">E25/E$23-1</f>
-        <v>0.0834863679979976</v>
+        <v>0.0729664561030206</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>805</v>
+        <v>846</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>2389.05310638326</v>
       </c>
       <c r="D26" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">tp_w_dcf*C26+(1-tp_w_dcf)*D26</f>
-        <v>2567.01299436215</v>
+        <v>2920.27491028345</v>
       </c>
       <c r="F26" s="14" t="n">
         <f aca="false">E26/E$23-1</f>
-        <v>0.0476593568096895</v>
+        <v>0.0416539184772755</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>1994.2738554254</v>
       </c>
       <c r="D27" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">tp_w_dcf*C27+(1-tp_w_dcf)*D27</f>
-        <v>2369.62336888322</v>
+        <v>2722.88528480452</v>
       </c>
       <c r="F27" s="14" t="n">
         <f aca="false">E27/E$23-1</f>
-        <v>-0.0329000671294738</v>
+        <v>-0.0287544105888852</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>809</v>
+        <v>850</v>
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>2155.49973345111</v>
       </c>
       <c r="D28" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">0.3*C28+(1-0.3)*D28</f>
-        <v>2568.13093767406</v>
+        <v>3062.69761996388</v>
       </c>
       <c r="F28" s="14" t="n">
         <f aca="false">E28/E$23-1</f>
-        <v>0.0481156161950842</v>
+        <v>0.0924557019314134</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>810</v>
+        <v>851</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>2155.49973345111</v>
       </c>
       <c r="D29" s="16" t="n">
-        <f aca="false">Val!B90</f>
-        <v>2744.97288234104</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>3451.49671418364</v>
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">0.7*C29+(1-0.7)*D29</f>
-        <v>2332.34167811809</v>
+        <v>2544.29882767086</v>
       </c>
       <c r="F29" s="14" t="n">
         <f aca="false">E29/E$23-1</f>
-        <v>-0.0481156161950842</v>
+        <v>-0.0924557019314135</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="C30" s="29" t="n">
+        <v>853</v>
+      </c>
+      <c r="C30" s="31" t="n">
         <f aca="false">C23-Val!B79</f>
         <v>0</v>
       </c>
@@ -46158,51 +47701,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>813</v>
+        <v>854</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>814</v>
+        <v>855</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>584</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>815</v>
+        <v>856</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>816</v>
+        <v>857</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>585</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>818</v>
+        <v>859</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>819</v>
+        <v>860</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>822</v>
+        <v>863</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>825</v>
+        <v>866</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>27</v>
@@ -46215,10 +47758,10 @@
       <c r="A4" s="0" t="s">
         <v>641</v>
       </c>
-      <c r="B4" s="30" t="n">
+      <c r="B4" s="32" t="n">
         <v>1121.28</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="32" t="n">
         <v>22.91</v>
       </c>
       <c r="D4" s="25" t="n">
@@ -46229,12 +47772,12 @@
         <f aca="false">D4-F4</f>
         <v>127.29</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="32" t="n">
         <v>1016.9</v>
       </c>
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
-      <c r="I4" s="30" t="n">
+      <c r="I4" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="14" t="n">
@@ -46257,37 +47800,37 @@
         <v>1</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>826</v>
+        <v>867</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>827</v>
+        <v>868</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>642</v>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="32" t="n">
         <v>921.47</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="32" t="n">
         <v>57.71</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">B5+C5</f>
         <v>979.18</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="32" t="n">
         <v>141.4</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="32" t="n">
         <v>837.77</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="32" t="n">
         <v>60.29</v>
       </c>
       <c r="H5" s="25"/>
-      <c r="I5" s="30" t="n">
+      <c r="I5" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="14" t="n">
@@ -46313,36 +47856,36 @@
         <v>224</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>828</v>
+        <v>869</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>643</v>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="32" t="n">
         <v>1322.05</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="32" t="n">
         <v>83.79</v>
       </c>
       <c r="D6" s="25" t="n">
         <f aca="false">B6+C6</f>
         <v>1405.84</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="32" t="n">
         <v>233.41</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="32" t="n">
         <v>1172.43</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="32" t="n">
         <v>87.21</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="14" t="n">
@@ -46368,36 +47911,36 @@
         <v>224</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>829</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>644</v>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="32" t="n">
         <v>1936.09</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="32" t="n">
         <v>105.56</v>
       </c>
       <c r="D7" s="25" t="n">
         <f aca="false">B7+C7</f>
         <v>2041.65</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="32" t="n">
         <v>326.25</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="32" t="n">
         <v>1715.4</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="32" t="n">
         <v>105.74</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="32" t="n">
         <v>13.83</v>
       </c>
-      <c r="I7" s="30" t="n">
+      <c r="I7" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="14" t="n">
@@ -46423,18 +47966,18 @@
         <v>224</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>830</v>
+        <v>871</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>831</v>
+        <v>872</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">ntd26_1q*opm26_1q</f>
         <v>658.9121</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="32" t="n">
         <v>28.83</v>
       </c>
       <c r="D8" s="25" t="n">
@@ -46445,12 +47988,12 @@
         <f aca="false">D8-F8</f>
         <v>115.2621</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="32" t="n">
         <v>572.48</v>
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="14" t="n">
@@ -46476,33 +48019,33 @@
         <v>128</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>832</v>
+        <v>873</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">ntd26_2q*opm26_2q</f>
         <v>766.03914</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="32" t="n">
         <v>95.83</v>
       </c>
       <c r="D9" s="25" t="n">
         <f aca="false">B9+C9</f>
         <v>861.86914</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="32" t="n">
         <v>155.65</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="32" t="n">
         <v>706.56</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="30" t="n">
+      <c r="I9" s="32" t="n">
         <v>63.2</v>
       </c>
       <c r="J9" s="14" t="n">
@@ -46525,35 +48068,35 @@
         <v>2</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>834</v>
+        <v>875</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>836</v>
-      </c>
-      <c r="B10" s="30" t="n">
+        <v>877</v>
+      </c>
+      <c r="B10" s="32" t="n">
         <v>876.45</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="32" t="n">
         <v>34.59</v>
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">B10+C10</f>
         <v>911.04</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="32" t="n">
         <v>147.7</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="32" t="n">
         <v>763.06</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
-      <c r="I10" s="30" t="n">
+      <c r="I10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="14" t="n">
@@ -46579,12 +48122,12 @@
         <v>224</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>837</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>838</v>
+        <v>879</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">SUM(B8:B10)</f>
@@ -46632,53 +48175,53 @@
         <v>128</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>839</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>841</v>
+        <v>882</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">(E6+E7+E11)/(D6+D7+D11)</f>
         <v>0.165580350953154</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>843</v>
+        <v>884</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11-I11)/(SUM(B4:B7)+B11)</f>
         <v>0.0481460113069807</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>844</v>
+        <v>885</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(1+B15)*(1-B14)</f>
         <v>0.874593626904623</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>846</v>
+        <v>887</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>847</v>
+        <v>888</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(F6+F7)/(B6+B7)</f>
@@ -46687,72 +48230,72 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">M11</f>
         <v>0.887328973543092</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>850</v>
+        <v>891</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">(F11-I11*(1-B14))/B11</f>
         <v>0.864414533026079</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>851</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>852</v>
+        <v>893</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">M5</f>
         <v>0.909166874667651</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>854</v>
+        <v>895</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11)/(SUM(B4:B7)+B11)</f>
         <v>0.0564592945007984</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>855</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>856</v>
+        <v>897</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">(1+B21)*(1-B14)</f>
         <v>0.881530393749635</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>857</v>
+        <v>898</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>858</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>859</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -46785,327 +48328,327 @@
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>860</v>
+        <v>901</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>861</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>862</v>
+        <v>903</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>863</v>
+        <v>904</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>867</v>
+        <v>908</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>868</v>
+        <v>909</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>869</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>871</v>
+        <v>912</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>872</v>
+        <v>913</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>873</v>
+        <v>914</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>874</v>
+        <v>915</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>875</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>876</v>
+        <v>917</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>877</v>
+        <v>918</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>878</v>
+        <v>919</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>879</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>880</v>
+        <v>921</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>881</v>
+        <v>922</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>883</v>
+        <v>924</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>885</v>
+        <v>926</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>887</v>
+        <v>928</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>888</v>
+        <v>929</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>890</v>
+        <v>931</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>892</v>
+        <v>933</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>893</v>
+        <v>934</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>897</v>
+        <v>938</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>899</v>
+        <v>940</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>900</v>
+        <v>941</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>901</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>904</v>
+        <v>945</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>907</v>
+        <v>948</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>908</v>
+        <v>949</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>909</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>910</v>
+        <v>951</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>912</v>
+        <v>953</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>913</v>
+        <v>954</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>914</v>
+        <v>955</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>915</v>
+        <v>956</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>916</v>
+        <v>957</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>917</v>
+        <v>958</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>918</v>
+        <v>959</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>920</v>
+        <v>961</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>921</v>
+        <v>962</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>922</v>
+        <v>963</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>923</v>
+        <v>964</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>924</v>
+        <v>965</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>925</v>
+        <v>966</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>928</v>
+        <v>969</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>934</v>
+        <v>975</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>935</v>
+        <v>976</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>936</v>
+        <v>977</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>937</v>
+        <v>978</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>938</v>
+        <v>979</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>939</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
